--- a/xlsx/country_comparison/.xlsx
+++ b/xlsx/country_comparison/.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -47,31 +47,35 @@
     <t xml:space="preserve">Japan</t>
   </si>
   <si>
+    <t xml:space="preserve">Russia</t>
+  </si>
+  <si>
     <t xml:space="preserve">Saudi Arabia</t>
   </si>
   <si>
     <t xml:space="preserve">USA</t>
   </si>
   <si>
-    <t xml:space="preserve">Supports tax on world top income to finance global poverty reduction
-(Any variant)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Affected by the top tax (any variant)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supports tax on world top 1% to finance global poverty reduction
+    <t xml:space="preserve">Supports the Global Climate Scheme (GCS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supports int'l tax on millionaires
+with 30% funding LICs (any variant)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accepts tax on world top 1% to finance global poverty reduction
 (Additional 15% tax on income over [$120k/year in PPP])</t>
   </si>
   <si>
-    <t xml:space="preserve">Affected by the top 1% tax (income &gt; $PPP 120k)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supports tax on world top 3% to finance global poverty reduction
-(Additional 15% tax over [$80k], 30% over [$120k], 45% over [$1M])</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Affected by the top 3% tax (income &gt; $PPP 80k)</t>
+    <t xml:space="preserve">Prefers sustainable future</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Governments should actively cooperate to have all countries
+converge in terms of GDP per capita by the end of the century"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Would support a global movement to tackle CC, tax millionaires,
+ and fund LICs (either petition, demonstrate, strike, or donate)</t>
   </si>
 </sst>
 </file>
@@ -440,251 +444,272 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="n">
-        <v>0.458655202633503</v>
+        <v>0.553352948193206</v>
       </c>
       <c r="C2" t="n">
-        <v>0.530633111073681</v>
+        <v>0.610914766632881</v>
       </c>
       <c r="D2" t="n">
-        <v>0.534615441391404</v>
+        <v>0.649673122291722</v>
       </c>
       <c r="E2" t="n">
-        <v>0.532199124020193</v>
+        <v>0.534385977368577</v>
       </c>
       <c r="F2" t="n">
-        <v>0.475339526743875</v>
+        <v>0.776272593268426</v>
       </c>
       <c r="G2" t="n">
-        <v>0.455066177183276</v>
+        <v>0.506505049421929</v>
       </c>
       <c r="H2" t="n">
-        <v>0.481053473314213</v>
+        <v>0.681637766424686</v>
       </c>
       <c r="I2" t="n">
-        <v>0.644527456241547</v>
+        <v>0.581054438205453</v>
       </c>
       <c r="J2" t="n">
-        <v>0.283838350853901</v>
+        <v>0.623284705512702</v>
       </c>
       <c r="K2" t="n">
-        <v>0.278766736483527</v>
+        <v>0.568474042011213</v>
       </c>
       <c r="L2" t="n">
-        <v>0.695880953418338</v>
+        <v>0.486313846276599</v>
       </c>
       <c r="M2" t="n">
-        <v>0.38602041410698</v>
+        <v>0.846671870687128</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.48666425997025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0591524213077198</v>
+        <v>0.704079856692946</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0407707508788973</v>
+        <v>0.735962846479202</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0323072107425518</v>
+        <v>0.751528818703853</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0266191432108494</v>
+        <v>0.735182627547195</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0508665529273163</v>
+        <v>0.82305515135296</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0154979588373725</v>
+        <v>0.669776585285023</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0308607490074744</v>
+        <v>0.730260714811827</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0702529813060691</v>
+        <v>0.698974698762325</v>
       </c>
       <c r="J3" t="n">
-        <v>0.114402739983896</v>
+        <v>0.623655467255751</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0300920300421565</v>
+        <v>0.663725304974921</v>
       </c>
       <c r="L3" t="n">
-        <v>0.213457131326528</v>
+        <v>0.737260039233821</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0779223306659385</v>
+        <v>0.830395038048113</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.658482304496079</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="n">
-        <v>0.528888358626659</v>
+        <v>0.693991148793208</v>
       </c>
       <c r="C4" t="n">
-        <v>0.623206921829844</v>
+        <v>0.727267133682238</v>
       </c>
       <c r="D4" t="n">
-        <v>0.662100661962385</v>
+        <v>0.713266166753258</v>
       </c>
       <c r="E4" t="n">
-        <v>0.645129138499509</v>
+        <v>0.722752212925052</v>
       </c>
       <c r="F4" t="n">
-        <v>0.652088141940814</v>
+        <v>0.839866307760825</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.694516301386687</v>
       </c>
       <c r="H4" t="n">
-        <v>0.595169320047074</v>
+        <v>0.727791884744065</v>
       </c>
       <c r="I4" t="n">
-        <v>0.581049693515047</v>
+        <v>0.671225049697161</v>
       </c>
       <c r="J4" t="n">
-        <v>0.460003610927742</v>
+        <v>0.603572620182626</v>
       </c>
       <c r="K4" t="n">
-        <v>0.321840723174092</v>
+        <v>0.691681993781983</v>
       </c>
       <c r="L4" t="n">
-        <v>0.656234738255263</v>
+        <v>0.754180914635801</v>
       </c>
       <c r="M4" t="n">
-        <v>0.466960372968151</v>
+        <v>0.817345461694808</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.622335501686223</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0324192263079185</v>
+        <v>0.680815013747804</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0228809019118487</v>
+        <v>0.701539116816613</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0152772811251959</v>
+        <v>0.721220700610068</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0158159265407275</v>
+        <v>0.703415187125182</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0364460596482764</v>
+        <v>0.759706650286704</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00635212756481645</v>
+        <v>0.575101001313061</v>
       </c>
       <c r="H5" t="n">
-        <v>0.013703147356521</v>
+        <v>0.731116681894394</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0382299828227781</v>
+        <v>0.68337742404715</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0699523880243387</v>
+        <v>0.659704988708263</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0195161254114759</v>
+        <v>0.759539408850822</v>
       </c>
       <c r="L5" t="n">
-        <v>0.136800251123575</v>
+        <v>0.689906588508866</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0397521568871045</v>
+        <v>0.721853509181885</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.618731104894089</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" t="n">
-        <v>0.432729011460262</v>
+        <v>0.704960018034767</v>
       </c>
       <c r="C6" t="n">
-        <v>0.494229631325223</v>
+        <v>0.780310385878786</v>
       </c>
       <c r="D6" t="n">
-        <v>0.494509481529061</v>
+        <v>0.767261516731427</v>
       </c>
       <c r="E6" t="n">
-        <v>0.482293276239211</v>
+        <v>0.757541746745335</v>
       </c>
       <c r="F6" t="n">
-        <v>0.377478972984925</v>
+        <v>0.874984008964506</v>
       </c>
       <c r="G6" t="n">
-        <v>0.317062120727541</v>
+        <v>0.847206298409435</v>
       </c>
       <c r="H6" t="n">
-        <v>0.446739876773781</v>
+        <v>0.842339547896952</v>
       </c>
       <c r="I6" t="n">
-        <v>0.666981999539339</v>
+        <v>0.65799487387268</v>
       </c>
       <c r="J6" t="n">
-        <v>0.204001758620865</v>
+        <v>0.656332785129309</v>
       </c>
       <c r="K6" t="n">
-        <v>0.259051167955435</v>
+        <v>0.703874631903231</v>
       </c>
       <c r="L6" t="n">
-        <v>0.713245760172143</v>
+        <v>0.777883926828007</v>
       </c>
       <c r="M6" t="n">
-        <v>0.359482567475819</v>
+        <v>0.92816201896394</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.562406199574745</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
-        <v>0.085037992635904</v>
+        <v>0.675595447215337</v>
       </c>
       <c r="C7" t="n">
-        <v>0.058871310106645</v>
+        <v>0.719216740354837</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0497557537097689</v>
+        <v>0.703425024778734</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0381284684121215</v>
+        <v>0.690418272415403</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0651357948522902</v>
+        <v>0.817088824971887</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0243920108908461</v>
+        <v>0.707832398863728</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0494954076529742</v>
+        <v>0.743080145118413</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0998345665218679</v>
+        <v>0.682786565268408</v>
       </c>
       <c r="J7" t="n">
-        <v>0.160672303258471</v>
+        <v>0.629978960602202</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0400180177711981</v>
+        <v>0.559364498889858</v>
       </c>
       <c r="L7" t="n">
-        <v>0.282886812048479</v>
+        <v>0.559364498889858</v>
       </c>
       <c r="M7" t="n">
-        <v>0.113725803486659</v>
+        <v>0.729122438104651</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.667115559981111</v>
       </c>
     </row>
   </sheetData>
